--- a/public/downloads/wadiz_a0010_tech_latest.xlsx
+++ b/public/downloads/wadiz_a0010_tech_latest.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>매주 토요일 08:00-09:00 (KST) 자동 실행</t>
+          <t>매주 토요일 20:00-21:00 (KST) · 한국 펀딩 트래픽 피크에 묻혀 봇 감지 최소화</t>
         </is>
       </c>
     </row>
